--- a/output/pdf_financials_xlsx/INNO.xlsx
+++ b/output/pdf_financials_xlsx/INNO.xlsx
@@ -2352,10 +2352,10 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="121">
@@ -4096,7 +4096,11 @@
           <t>Issuance of common shares, net of issuance cost</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
